--- a/data2026.xlsx
+++ b/data2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melan\DESU_DATA_2026\ProjetNR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CA52BF-E62D-453E-BF93-84A66E69BA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44273B67-B6B7-41EB-8950-54CC0F6F0D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A5577CF9-A2EC-4381-9165-1BFB57234FC3}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5872" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5864" uniqueCount="661">
   <si>
     <t>Patient</t>
   </si>
@@ -8895,7 +8895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9E9E3CB-BB82-4E38-9625-63F9049E9733}">
-  <dimension ref="A1:S86"/>
+  <dimension ref="A1:R86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.453125" style="51" bestFit="1" customWidth="1"/>
@@ -8916,7 +8916,7 @@
     <col min="19" max="19" width="31.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -9027,11 +9027,8 @@
       <c r="R2" s="126" t="s">
         <v>554</v>
       </c>
-      <c r="S2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="51" t="s">
         <v>8</v>
       </c>
@@ -9086,11 +9083,8 @@
       <c r="R3" s="126" t="s">
         <v>552</v>
       </c>
-      <c r="S3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="51" t="s">
         <v>69</v>
       </c>
@@ -9145,11 +9139,8 @@
       <c r="R4" s="126" t="s">
         <v>555</v>
       </c>
-      <c r="S4" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="51" t="s">
         <v>29</v>
       </c>
@@ -9204,11 +9195,8 @@
       <c r="R5" s="126" t="s">
         <v>556</v>
       </c>
-      <c r="S5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="51" t="s">
         <v>30</v>
       </c>
@@ -9263,11 +9251,8 @@
       <c r="R6" s="126" t="s">
         <v>556</v>
       </c>
-      <c r="S6" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="51" t="s">
         <v>12</v>
       </c>
@@ -9322,11 +9307,8 @@
       <c r="R7" s="126" t="s">
         <v>559</v>
       </c>
-      <c r="S7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="51" t="s">
         <v>14</v>
       </c>
@@ -9381,11 +9363,8 @@
       <c r="R8" s="126" t="s">
         <v>560</v>
       </c>
-      <c r="S8" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="51" t="s">
         <v>31</v>
       </c>
@@ -9440,11 +9419,8 @@
       <c r="R9" s="127" t="s">
         <v>552</v>
       </c>
-      <c r="S9" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="51" t="s">
         <v>33</v>
       </c>
@@ -9500,7 +9476,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="51" t="s">
         <v>35</v>
       </c>
@@ -9556,7 +9532,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="51" t="s">
         <v>37</v>
       </c>
@@ -9612,7 +9588,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="51" t="s">
         <v>38</v>
       </c>
@@ -9668,7 +9644,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="51" t="s">
         <v>39</v>
       </c>
@@ -9724,7 +9700,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="51" t="s">
         <v>40</v>
       </c>
@@ -9780,7 +9756,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="51" t="s">
         <v>25</v>
       </c>

--- a/data2026.xlsx
+++ b/data2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melan\DESU_DATA_2026\ProjetNR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44273B67-B6B7-41EB-8950-54CC0F6F0D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D96EF0-DBA9-407E-A71D-4F8CBAAF8E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A5577CF9-A2EC-4381-9165-1BFB57234FC3}"/>
   </bookViews>
@@ -9078,10 +9078,10 @@
         <v>103</v>
       </c>
       <c r="Q3" s="126" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R3" s="126" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -9414,10 +9414,10 @@
         <v>118</v>
       </c>
       <c r="Q9" s="127" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R9" s="127" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
@@ -9582,10 +9582,10 @@
         <v>72</v>
       </c>
       <c r="Q12" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R12" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
@@ -9638,10 +9638,10 @@
         <v>72</v>
       </c>
       <c r="Q13" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R13" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -9694,10 +9694,10 @@
         <v>97</v>
       </c>
       <c r="Q14" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R14" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
@@ -9750,10 +9750,10 @@
         <v>97</v>
       </c>
       <c r="Q15" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R15" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -9806,10 +9806,10 @@
         <v>112</v>
       </c>
       <c r="Q16" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R16" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
@@ -9862,10 +9862,10 @@
         <v>118</v>
       </c>
       <c r="Q17" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R17" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
@@ -9918,10 +9918,10 @@
         <v>103</v>
       </c>
       <c r="Q18" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R18" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
@@ -10030,10 +10030,10 @@
         <v>100</v>
       </c>
       <c r="Q20" s="127" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R20" s="127" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
@@ -10089,7 +10089,7 @@
         <v>1</v>
       </c>
       <c r="R21" s="128" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
@@ -10198,10 +10198,10 @@
         <v>106</v>
       </c>
       <c r="Q23" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R23" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
@@ -10310,7 +10310,7 @@
         <v>100</v>
       </c>
       <c r="Q25" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R25" s="129" t="s">
         <v>563</v>
@@ -10366,10 +10366,10 @@
         <v>106</v>
       </c>
       <c r="Q26" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R26" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
@@ -10590,10 +10590,10 @@
         <v>68</v>
       </c>
       <c r="Q30" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R30" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
@@ -10646,10 +10646,10 @@
         <v>68</v>
       </c>
       <c r="Q31" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R31" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
@@ -10761,7 +10761,7 @@
         <v>0.93</v>
       </c>
       <c r="R33" s="159" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.35">
@@ -10814,10 +10814,10 @@
         <v>109</v>
       </c>
       <c r="Q34" s="128" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R34" s="128" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10926,10 +10926,10 @@
         <v>103</v>
       </c>
       <c r="Q36" s="128" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R36" s="128" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
@@ -11038,10 +11038,10 @@
         <v>100</v>
       </c>
       <c r="Q38" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R38" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.35">
@@ -11150,7 +11150,7 @@
         <v>100</v>
       </c>
       <c r="Q40" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R40" s="129" t="s">
         <v>562</v>
@@ -11206,7 +11206,7 @@
         <v>100</v>
       </c>
       <c r="Q41" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R41" s="129" t="s">
         <v>563</v>
@@ -11262,10 +11262,10 @@
         <v>100</v>
       </c>
       <c r="Q42" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R42" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.35">
@@ -11318,10 +11318,10 @@
         <v>100</v>
       </c>
       <c r="Q43" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R43" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.35">
@@ -11374,10 +11374,10 @@
         <v>118</v>
       </c>
       <c r="Q44" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R44" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.35">
@@ -11542,10 +11542,10 @@
         <v>97</v>
       </c>
       <c r="Q47" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R47" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.35">
@@ -11598,10 +11598,10 @@
         <v>97</v>
       </c>
       <c r="Q48" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R48" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.35">
@@ -11710,10 +11710,10 @@
         <v>112</v>
       </c>
       <c r="Q50" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R50" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.35">
@@ -11766,10 +11766,10 @@
         <v>72</v>
       </c>
       <c r="Q51" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R51" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.35">
@@ -11822,10 +11822,10 @@
         <v>72</v>
       </c>
       <c r="Q52" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R52" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.35">
@@ -11878,10 +11878,10 @@
         <v>121</v>
       </c>
       <c r="Q53" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R53" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.35">
@@ -11934,10 +11934,10 @@
         <v>118</v>
       </c>
       <c r="Q54" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R54" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.35">
@@ -12046,10 +12046,10 @@
         <v>103</v>
       </c>
       <c r="Q56" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R56" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.35">
@@ -12158,10 +12158,10 @@
         <v>100</v>
       </c>
       <c r="Q58" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
       <c r="R58" s="129" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.35">
@@ -12273,7 +12273,7 @@
         <v>0.93</v>
       </c>
       <c r="R60" s="159" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.35">
@@ -12329,7 +12329,7 @@
         <v>1</v>
       </c>
       <c r="R61" s="128" t="s">
-        <v>552</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.35">

--- a/data2026.xlsx
+++ b/data2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melan\DESU_DATA_2026\ProjetNR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D96EF0-DBA9-407E-A71D-4F8CBAAF8E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC4BDBD-95A1-4CC6-9495-57D6BB720AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A5577CF9-A2EC-4381-9165-1BFB57234FC3}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5864" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5788" uniqueCount="661">
   <si>
     <t>Patient</t>
   </si>
@@ -8895,7 +8895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9E9E3CB-BB82-4E38-9625-63F9049E9733}">
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.453125" style="51" bestFit="1" customWidth="1"/>
@@ -10478,10 +10478,10 @@
         <v>97</v>
       </c>
       <c r="Q28" s="129" t="s">
-        <v>567</v>
+        <v>68</v>
       </c>
       <c r="R28" s="129" t="s">
-        <v>567</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
@@ -11845,7 +11845,7 @@
         <v>-276.39999999999998</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>331</v>
+        <v>572</v>
       </c>
       <c r="G53" s="12">
         <v>0</v>
@@ -11990,10 +11990,10 @@
         <v>97</v>
       </c>
       <c r="Q55" s="129" t="s">
-        <v>567</v>
+        <v>68</v>
       </c>
       <c r="R55" s="129" t="s">
-        <v>567</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.35">
@@ -12381,6 +12381,12 @@
       <c r="P62" s="5">
         <v>106</v>
       </c>
+      <c r="Q62" s="129" t="s">
+        <v>68</v>
+      </c>
+      <c r="R62" s="129" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" s="165" t="s">
@@ -12431,6 +12437,12 @@
       <c r="P63" s="167">
         <v>91</v>
       </c>
+      <c r="Q63" s="129" t="s">
+        <v>68</v>
+      </c>
+      <c r="R63" s="129" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" s="51" t="s">
@@ -12481,6 +12493,12 @@
       <c r="P64" s="5">
         <v>109</v>
       </c>
+      <c r="Q64" s="129" t="s">
+        <v>68</v>
+      </c>
+      <c r="R64" s="129" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="65" spans="1:18" s="112" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="51" t="s">
@@ -12531,8 +12549,12 @@
       <c r="P65" s="5">
         <v>112</v>
       </c>
-      <c r="Q65" s="88"/>
-      <c r="R65" s="88"/>
+      <c r="Q65" s="129" t="s">
+        <v>68</v>
+      </c>
+      <c r="R65" s="129" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" s="51" t="s">
@@ -12583,819 +12605,24 @@
       <c r="P66" s="5">
         <v>85</v>
       </c>
+      <c r="Q66" s="129" t="s">
+        <v>68</v>
+      </c>
+      <c r="R66" s="129" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A67" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="B67" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" s="57"/>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="59">
-        <v>92</v>
-      </c>
-      <c r="I67" s="59">
-        <v>98</v>
-      </c>
-      <c r="J67" s="59">
-        <v>92</v>
-      </c>
-      <c r="K67" s="59">
-        <v>86</v>
-      </c>
-      <c r="L67" s="59">
-        <v>100</v>
-      </c>
-      <c r="M67" s="59">
-        <v>89</v>
-      </c>
-      <c r="N67" s="59">
-        <v>82</v>
-      </c>
-      <c r="O67" s="59">
-        <v>98</v>
-      </c>
-      <c r="P67" s="59">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A68" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="57"/>
-      <c r="D68" s="57"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="59">
-        <v>92</v>
-      </c>
-      <c r="I68" s="59">
-        <v>98</v>
-      </c>
-      <c r="J68" s="59">
-        <v>92</v>
-      </c>
-      <c r="K68" s="59">
-        <v>86</v>
-      </c>
-      <c r="L68" s="59">
-        <v>100</v>
-      </c>
-      <c r="M68" s="59">
-        <v>89</v>
-      </c>
-      <c r="N68" s="59">
-        <v>82</v>
-      </c>
-      <c r="O68" s="59">
-        <v>98</v>
-      </c>
-      <c r="P68" s="59">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A69" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="B69" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="57"/>
-      <c r="D69" s="57"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="57"/>
-      <c r="G69" s="57"/>
-      <c r="H69" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="I69" s="57">
-        <v>93</v>
-      </c>
-      <c r="J69" s="57">
-        <v>91</v>
-      </c>
-      <c r="K69" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="L69" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="M69" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="N69" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="O69" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="P69" s="57" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A70" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="B70" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" s="57"/>
-      <c r="D70" s="57"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="59">
-        <v>88</v>
-      </c>
-      <c r="I70" s="59">
-        <v>86</v>
-      </c>
-      <c r="J70" s="59">
-        <v>82</v>
-      </c>
-      <c r="K70" s="59">
-        <v>94</v>
-      </c>
-      <c r="L70" s="59">
-        <v>105</v>
-      </c>
-      <c r="M70" s="59">
-        <v>99</v>
-      </c>
-      <c r="N70" s="59">
-        <v>115</v>
-      </c>
-      <c r="O70" s="59">
-        <v>104</v>
-      </c>
-      <c r="P70" s="59" cm="1">
-        <f t="array" aca="1" ref="P70" ca="1">H70:P71113</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A71" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="57"/>
-      <c r="D71" s="57"/>
-      <c r="E71" s="57"/>
-      <c r="F71" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H71" s="8">
-        <v>88</v>
-      </c>
-      <c r="I71" s="8">
-        <v>86</v>
-      </c>
-      <c r="J71" s="8">
-        <v>82</v>
-      </c>
-      <c r="K71" s="8">
-        <v>94</v>
-      </c>
-      <c r="L71" s="8">
-        <v>105</v>
-      </c>
-      <c r="M71" s="8">
-        <v>99</v>
-      </c>
-      <c r="N71" s="8">
-        <v>115</v>
-      </c>
-      <c r="O71" s="8">
-        <v>104</v>
-      </c>
-      <c r="P71" s="8">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A72" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="B72" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="57"/>
-      <c r="D72" s="57"/>
-      <c r="E72" s="57"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57">
-        <v>51</v>
-      </c>
-      <c r="I72" s="57">
-        <v>55</v>
-      </c>
-      <c r="J72" s="57">
-        <v>51</v>
-      </c>
-      <c r="K72" s="57">
-        <v>56</v>
-      </c>
-      <c r="L72" s="57">
-        <v>50</v>
-      </c>
-      <c r="M72" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="N72" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="O72" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="P72" s="57" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A73" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="B73" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" s="57"/>
-      <c r="D73" s="57"/>
-      <c r="E73" s="57"/>
-      <c r="F73" s="57"/>
-      <c r="G73" s="57"/>
-      <c r="H73" s="59">
-        <v>80</v>
-      </c>
-      <c r="I73" s="59">
-        <v>81</v>
-      </c>
-      <c r="J73" s="59">
-        <v>76</v>
-      </c>
-      <c r="K73" s="59">
-        <v>76</v>
-      </c>
-      <c r="L73" s="59">
-        <v>68</v>
-      </c>
-      <c r="M73" s="59">
-        <v>105</v>
-      </c>
-      <c r="N73" s="59">
-        <v>112</v>
-      </c>
-      <c r="O73" s="59">
-        <v>110</v>
-      </c>
-      <c r="P73" s="59">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A74" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="B74" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="57"/>
-      <c r="D74" s="57"/>
-      <c r="E74" s="57"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="59">
-        <v>80</v>
-      </c>
-      <c r="I74" s="59">
-        <v>81</v>
-      </c>
-      <c r="J74" s="59">
-        <v>76</v>
-      </c>
-      <c r="K74" s="59">
-        <v>76</v>
-      </c>
-      <c r="L74" s="59">
-        <v>68</v>
-      </c>
-      <c r="M74" s="59">
-        <v>105</v>
-      </c>
-      <c r="N74" s="59">
-        <v>112</v>
-      </c>
-      <c r="O74" s="59">
-        <v>110</v>
-      </c>
-      <c r="P74" s="59">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A75" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="B75" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C75" s="57"/>
-      <c r="D75" s="57"/>
-      <c r="E75" s="57"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57">
-        <v>86</v>
-      </c>
-      <c r="I75" s="57">
-        <v>82</v>
-      </c>
-      <c r="J75" s="57">
-        <v>94</v>
-      </c>
-      <c r="K75" s="57">
-        <v>86</v>
-      </c>
-      <c r="L75" s="57">
-        <v>100</v>
-      </c>
-      <c r="M75" s="57">
-        <v>79</v>
-      </c>
-      <c r="N75" s="57">
-        <v>91</v>
-      </c>
-      <c r="O75" s="57">
-        <v>69</v>
-      </c>
-      <c r="P75" s="57">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A76" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="B76" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C76" s="57"/>
-      <c r="D76" s="57"/>
-      <c r="E76" s="57"/>
-      <c r="F76" s="57"/>
-      <c r="G76" s="57"/>
-      <c r="H76" s="57">
-        <v>50</v>
-      </c>
-      <c r="I76" s="57">
-        <v>63</v>
-      </c>
-      <c r="J76" s="57">
-        <v>64</v>
-      </c>
-      <c r="K76" s="57">
-        <v>55</v>
-      </c>
-      <c r="L76" s="57">
-        <v>55</v>
-      </c>
-      <c r="M76" s="57">
-        <v>89</v>
-      </c>
-      <c r="N76" s="57">
-        <v>100</v>
-      </c>
-      <c r="O76" s="57">
-        <v>84</v>
-      </c>
-      <c r="P76" s="57">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A77" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="B77" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C77" s="57"/>
-      <c r="D77" s="57"/>
-      <c r="E77" s="57"/>
-      <c r="F77" s="57"/>
-      <c r="G77" s="57"/>
-      <c r="H77" s="57">
-        <v>73</v>
-      </c>
-      <c r="I77" s="57">
-        <v>75</v>
-      </c>
-      <c r="J77" s="57">
-        <v>82</v>
-      </c>
-      <c r="K77" s="57">
-        <v>71</v>
-      </c>
-      <c r="L77" s="57">
-        <v>86</v>
-      </c>
-      <c r="M77" s="57">
-        <v>94</v>
-      </c>
-      <c r="N77" s="57">
-        <v>97</v>
-      </c>
-      <c r="O77" s="57">
-        <v>96</v>
-      </c>
-      <c r="P77" s="57">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A78" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="B78" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C78" s="57"/>
-      <c r="D78" s="57"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="57"/>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="I78" s="57">
-        <v>93</v>
-      </c>
-      <c r="J78" s="57">
-        <v>91</v>
-      </c>
-      <c r="K78" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="L78" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="M78" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="N78" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="O78" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="P78" s="57" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A79" s="55" t="s">
-        <v>81</v>
-      </c>
-      <c r="B79" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C79" s="57"/>
-      <c r="D79" s="57"/>
-      <c r="E79" s="57"/>
-      <c r="F79" s="57"/>
-      <c r="G79" s="57"/>
-      <c r="H79" s="57">
-        <v>94</v>
-      </c>
-      <c r="I79" s="57">
-        <v>91</v>
-      </c>
-      <c r="J79" s="57">
-        <v>98</v>
-      </c>
-      <c r="K79" s="57">
-        <v>88</v>
-      </c>
-      <c r="L79" s="57">
-        <v>94</v>
-      </c>
-      <c r="M79" s="57">
-        <v>114</v>
-      </c>
-      <c r="N79" s="57">
-        <v>112</v>
-      </c>
-      <c r="O79" s="57">
-        <v>110</v>
-      </c>
-      <c r="P79" s="57">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A80" s="55" t="s">
-        <v>86</v>
-      </c>
-      <c r="B80" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C80" s="57"/>
-      <c r="D80" s="57"/>
-      <c r="E80" s="57"/>
-      <c r="F80" s="57"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="57">
-        <v>86</v>
-      </c>
-      <c r="I80" s="57">
-        <v>92</v>
-      </c>
-      <c r="J80" s="57">
-        <v>94</v>
-      </c>
-      <c r="K80" s="57">
-        <v>77</v>
-      </c>
-      <c r="L80" s="57">
-        <v>89</v>
-      </c>
-      <c r="M80" s="57">
-        <v>94</v>
-      </c>
-      <c r="N80" s="57">
-        <v>91</v>
-      </c>
-      <c r="O80" s="57">
-        <v>91</v>
-      </c>
-      <c r="P80" s="57">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A81" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="B81" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
-      <c r="E81" s="57"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57">
-        <v>71</v>
-      </c>
-      <c r="I81" s="57">
-        <v>81</v>
-      </c>
-      <c r="J81" s="57">
-        <v>84</v>
-      </c>
-      <c r="K81" s="57">
-        <v>74</v>
-      </c>
-      <c r="L81" s="57">
-        <v>64</v>
-      </c>
-      <c r="M81" s="57">
-        <v>97</v>
-      </c>
-      <c r="N81" s="57">
-        <v>109</v>
-      </c>
-      <c r="O81" s="57">
-        <v>93</v>
-      </c>
-      <c r="P81" s="57">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A82" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="B82" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57"/>
-      <c r="E82" s="57"/>
-      <c r="F82" s="57"/>
-      <c r="G82" s="57"/>
-      <c r="H82" s="57">
-        <v>51</v>
-      </c>
-      <c r="I82" s="57">
-        <v>55</v>
-      </c>
-      <c r="J82" s="57">
-        <v>51</v>
-      </c>
-      <c r="K82" s="57">
-        <v>56</v>
-      </c>
-      <c r="L82" s="57">
-        <v>50</v>
-      </c>
-      <c r="M82" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="N82" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="O82" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="P82" s="57" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A83" s="55" t="s">
-        <v>94</v>
-      </c>
-      <c r="B83" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C83" s="57"/>
-      <c r="D83" s="57"/>
-      <c r="E83" s="57"/>
-      <c r="F83" s="57"/>
-      <c r="G83" s="57"/>
-      <c r="H83" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="I83" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="J83" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="K83" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="L83" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="M83" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="N83" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="O83" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="P83" s="57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A84" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="B84" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C84" s="57"/>
-      <c r="D84" s="57"/>
-      <c r="E84" s="57"/>
-      <c r="F84" s="57"/>
-      <c r="G84" s="57"/>
-      <c r="H84" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="I84" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="J84" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="K84" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="L84" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="M84" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="N84" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="O84" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="P84" s="57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A85" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="B85" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C85" s="57"/>
-      <c r="D85" s="57"/>
-      <c r="E85" s="57"/>
-      <c r="F85" s="57"/>
-      <c r="G85" s="57"/>
-      <c r="H85" s="57">
-        <v>90</v>
-      </c>
-      <c r="I85" s="57">
-        <v>94</v>
-      </c>
-      <c r="J85" s="57">
-        <v>70</v>
-      </c>
-      <c r="K85" s="57">
-        <v>112</v>
-      </c>
-      <c r="L85" s="57">
-        <v>100</v>
-      </c>
-      <c r="M85" s="57">
-        <v>111</v>
-      </c>
-      <c r="N85" s="57">
-        <v>91</v>
-      </c>
-      <c r="O85" s="57">
-        <v>89</v>
-      </c>
-      <c r="P85" s="57">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A86" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="B86" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C86" s="57"/>
-      <c r="D86" s="57"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="57"/>
-      <c r="H86" s="57">
-        <v>96</v>
-      </c>
-      <c r="I86" s="57">
-        <v>95</v>
-      </c>
-      <c r="J86" s="57">
-        <v>99</v>
-      </c>
-      <c r="K86" s="57">
-        <v>98</v>
-      </c>
-      <c r="L86" s="57">
-        <v>105</v>
-      </c>
-      <c r="M86" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="N86" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="O86" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="P86" s="57" t="s">
-        <v>350</v>
-      </c>
+      <c r="Q67" s="129"/>
+      <c r="R67" s="129"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A61 A62:B62 A63:A83 B75:B80 B83 A84:B84 B85:B86 A85:A1048576">
+  <conditionalFormatting sqref="A1:A61 A62:B62 A63:A1048576">
     <cfRule type="containsText" dxfId="13" priority="11" operator="containsText" text="ok">
       <formula>NOT(ISERROR(SEARCH("ok",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H49:O49 P59:P74">
+  <conditionalFormatting sqref="H49:O49 P59:P66">
     <cfRule type="containsText" dxfId="12" priority="8" operator="containsText" text="NI">
       <formula>NOT(ISERROR(SEARCH("NI",H49)))</formula>
     </cfRule>
